--- a/6.Profile Insights/Salary Details.xlsx
+++ b/6.Profile Insights/Salary Details.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenova\OneDrive\Desktop\TestingDocumentation\Profile Insights\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenova\Desktop\TestingDocumentation\6.Profile Insights\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D24FD60-AB1B-4FED-A53F-EB47BFB698E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E270190F-4122-4649-B4DC-E320ECD130AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4365" yWindow="4095" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Current CTC Breakdown" sheetId="1" r:id="rId1"/>
@@ -275,7 +275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -318,6 +318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1064,7 +1065,7 @@
         <f>'Current CTC Breakdown'!I16</f>
         <v>476756</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="18">
         <f>B2/100000</f>
         <v>4.7675599999999996</v>
       </c>
